--- a/flashcard_template.xlsx
+++ b/flashcard_template.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD6239B-529D-4D7C-8F5F-775F66E02005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F7A5D4-07F1-43E9-9B37-B9276254399F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
     <sheet name="Buổi 3" sheetId="2" r:id="rId2"/>
     <sheet name="Buổi 4" sheetId="3" r:id="rId3"/>
+    <sheet name="New" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="654">
   <si>
     <t>English</t>
   </si>
@@ -1952,6 +1953,33 @@
   </si>
   <si>
     <t>row</t>
+  </si>
+  <si>
+    <t>shade</t>
+  </si>
+  <si>
+    <t>..</t>
+  </si>
+  <si>
+    <t>bóng mát</t>
+  </si>
+  <si>
+    <t>stairs</t>
+  </si>
+  <si>
+    <t>cầu thang</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>sân khấu</t>
+  </si>
+  <si>
+    <t>tent</t>
+  </si>
+  <si>
+    <t>lều</t>
   </si>
 </sst>
 </file>
@@ -2432,7 +2460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2440,7 +2468,7 @@
     <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2457,7 +2485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>309</v>
       </c>
@@ -2474,7 +2502,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>310</v>
       </c>
@@ -2491,7 +2519,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>311</v>
       </c>
@@ -2508,7 +2536,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>312</v>
       </c>
@@ -2525,7 +2553,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>313</v>
       </c>
@@ -2542,7 +2570,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>314</v>
       </c>
@@ -2559,7 +2587,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>315</v>
       </c>
@@ -2576,7 +2604,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>316</v>
       </c>
@@ -2593,7 +2621,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>317</v>
       </c>
@@ -2610,7 +2638,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>320</v>
       </c>
@@ -2627,7 +2655,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>323</v>
       </c>
@@ -2644,7 +2672,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>325</v>
       </c>
@@ -2661,7 +2689,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>327</v>
       </c>
@@ -2678,7 +2706,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>329</v>
       </c>
@@ -2695,7 +2723,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>330</v>
       </c>
@@ -2712,7 +2740,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>332</v>
       </c>
@@ -2729,7 +2757,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>334</v>
       </c>
@@ -2746,7 +2774,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>335</v>
       </c>
@@ -2763,7 +2791,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>336</v>
       </c>
@@ -2780,7 +2808,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>338</v>
       </c>
@@ -2797,7 +2825,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>341</v>
       </c>
@@ -2814,7 +2842,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>344</v>
       </c>
@@ -2831,7 +2859,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>347</v>
       </c>
@@ -2848,7 +2876,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>348</v>
       </c>
@@ -2865,7 +2893,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>351</v>
       </c>
@@ -2882,7 +2910,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>353</v>
       </c>
@@ -2899,7 +2927,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>354</v>
       </c>
@@ -2916,7 +2944,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>355</v>
       </c>
@@ -2933,7 +2961,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>358</v>
       </c>
@@ -2950,7 +2978,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>359</v>
       </c>
@@ -2967,7 +2995,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>362</v>
       </c>
@@ -2984,7 +3012,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>364</v>
       </c>
@@ -3001,7 +3029,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>365</v>
       </c>
@@ -3018,7 +3046,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>367</v>
       </c>
@@ -3035,7 +3063,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>368</v>
       </c>
@@ -3052,7 +3080,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>370</v>
       </c>
@@ -3069,7 +3097,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>372</v>
       </c>
@@ -3086,7 +3114,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>374</v>
       </c>
@@ -3103,7 +3131,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>377</v>
       </c>
@@ -3120,7 +3148,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>379</v>
       </c>
@@ -3137,7 +3165,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>382</v>
       </c>
@@ -3154,7 +3182,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>385</v>
       </c>
@@ -3171,7 +3199,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>387</v>
       </c>
@@ -3188,7 +3216,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>388</v>
       </c>
@@ -3205,7 +3233,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>391</v>
       </c>
@@ -3222,7 +3250,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>393</v>
       </c>
@@ -3239,7 +3267,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>395</v>
       </c>
@@ -3256,7 +3284,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>397</v>
       </c>
@@ -3273,7 +3301,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>398</v>
       </c>
@@ -3290,7 +3318,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>401</v>
       </c>
@@ -3316,7 +3344,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -3324,7 +3352,7 @@
     <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3341,7 +3369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>204</v>
       </c>
@@ -3358,7 +3386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>205</v>
       </c>
@@ -3375,7 +3403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>206</v>
       </c>
@@ -3392,7 +3420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>207</v>
       </c>
@@ -3409,7 +3437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>208</v>
       </c>
@@ -3426,7 +3454,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>209</v>
       </c>
@@ -3443,7 +3471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>210</v>
       </c>
@@ -3460,7 +3488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>211</v>
       </c>
@@ -3477,7 +3505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>212</v>
       </c>
@@ -3494,7 +3522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>213</v>
       </c>
@@ -3511,7 +3539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>214</v>
       </c>
@@ -3528,7 +3556,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>215</v>
       </c>
@@ -3545,7 +3573,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>216</v>
       </c>
@@ -3562,7 +3590,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>217</v>
       </c>
@@ -3579,7 +3607,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>218</v>
       </c>
@@ -3596,7 +3624,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>219</v>
       </c>
@@ -3613,7 +3641,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>220</v>
       </c>
@@ -3630,7 +3658,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>221</v>
       </c>
@@ -3647,7 +3675,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>222</v>
       </c>
@@ -3664,7 +3692,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>223</v>
       </c>
@@ -3681,7 +3709,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>224</v>
       </c>
@@ -3698,7 +3726,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>225</v>
       </c>
@@ -3715,7 +3743,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>253</v>
       </c>
@@ -3732,7 +3760,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>226</v>
       </c>
@@ -3749,7 +3777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>227</v>
       </c>
@@ -3766,7 +3794,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>228</v>
       </c>
@@ -3783,7 +3811,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>229</v>
       </c>
@@ -3800,7 +3828,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>230</v>
       </c>
@@ -3817,7 +3845,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>231</v>
       </c>
@@ -3834,7 +3862,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>232</v>
       </c>
@@ -3851,7 +3879,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>233</v>
       </c>
@@ -3868,7 +3896,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>234</v>
       </c>
@@ -3885,7 +3913,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>235</v>
       </c>
@@ -3902,7 +3930,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>236</v>
       </c>
@@ -3919,7 +3947,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>237</v>
       </c>
@@ -3936,7 +3964,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>238</v>
       </c>
@@ -3953,7 +3981,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>239</v>
       </c>
@@ -3970,7 +3998,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>240</v>
       </c>
@@ -3987,7 +4015,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>241</v>
       </c>
@@ -4004,7 +4032,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>242</v>
       </c>
@@ -4021,7 +4049,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>243</v>
       </c>
@@ -4038,7 +4066,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>244</v>
       </c>
@@ -4055,7 +4083,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>245</v>
       </c>
@@ -4072,7 +4100,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>246</v>
       </c>
@@ -4089,7 +4117,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>247</v>
       </c>
@@ -4106,7 +4134,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>248</v>
       </c>
@@ -4123,7 +4151,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>249</v>
       </c>
@@ -4140,7 +4168,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>250</v>
       </c>
@@ -4157,7 +4185,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>251</v>
       </c>
@@ -4174,7 +4202,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>252</v>
       </c>
@@ -4200,7 +4228,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6730DBEC-D7FD-4C91-8451-FD627D0E4262}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4208,7 +4236,7 @@
     <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4225,7 +4253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>596</v>
       </c>
@@ -4242,7 +4270,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>309</v>
       </c>
@@ -4259,7 +4287,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>597</v>
       </c>
@@ -4276,7 +4304,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>598</v>
       </c>
@@ -4293,7 +4321,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>599</v>
       </c>
@@ -4310,7 +4338,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>600</v>
       </c>
@@ -4327,7 +4355,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>601</v>
       </c>
@@ -4344,7 +4372,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>602</v>
       </c>
@@ -4361,7 +4389,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>603</v>
       </c>
@@ -4378,7 +4406,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>604</v>
       </c>
@@ -4395,7 +4423,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>605</v>
       </c>
@@ -4412,7 +4440,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>606</v>
       </c>
@@ -4429,7 +4457,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>607</v>
       </c>
@@ -4446,7 +4474,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>608</v>
       </c>
@@ -4463,7 +4491,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>609</v>
       </c>
@@ -4480,7 +4508,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>610</v>
       </c>
@@ -4497,7 +4525,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>611</v>
       </c>
@@ -4514,7 +4542,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>612</v>
       </c>
@@ -4531,7 +4559,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>613</v>
       </c>
@@ -4548,7 +4576,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>614</v>
       </c>
@@ -4565,7 +4593,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>615</v>
       </c>
@@ -4582,7 +4610,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>616</v>
       </c>
@@ -4599,7 +4627,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>617</v>
       </c>
@@ -4616,7 +4644,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>618</v>
       </c>
@@ -4633,7 +4661,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>619</v>
       </c>
@@ -4650,7 +4678,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>620</v>
       </c>
@@ -4667,7 +4695,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>621</v>
       </c>
@@ -4684,7 +4712,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>622</v>
       </c>
@@ -4701,7 +4729,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>623</v>
       </c>
@@ -4718,7 +4746,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>624</v>
       </c>
@@ -4735,7 +4763,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>625</v>
       </c>
@@ -4752,7 +4780,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>626</v>
       </c>
@@ -4769,7 +4797,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>627</v>
       </c>
@@ -4786,7 +4814,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>628</v>
       </c>
@@ -4803,7 +4831,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>629</v>
       </c>
@@ -4820,7 +4848,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>630</v>
       </c>
@@ -4837,7 +4865,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>631</v>
       </c>
@@ -4854,7 +4882,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>632</v>
       </c>
@@ -4871,7 +4899,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>633</v>
       </c>
@@ -4888,7 +4916,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>634</v>
       </c>
@@ -4905,7 +4933,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>635</v>
       </c>
@@ -4922,7 +4950,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>636</v>
       </c>
@@ -4939,7 +4967,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>637</v>
       </c>
@@ -4956,7 +4984,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>638</v>
       </c>
@@ -4973,7 +5001,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>639</v>
       </c>
@@ -4990,7 +5018,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>640</v>
       </c>
@@ -5007,7 +5035,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>641</v>
       </c>
@@ -5024,7 +5052,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>642</v>
       </c>
@@ -5041,7 +5069,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>643</v>
       </c>
@@ -5058,7 +5086,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>644</v>
       </c>
@@ -5074,6 +5102,411 @@
       <c r="E51" s="2" t="s">
         <v>595</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB905D0-5FC0-49F8-9009-8F91F0A4360C}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/flashcard_template.xlsx
+++ b/flashcard_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F7A5D4-07F1-43E9-9B37-B9276254399F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC37B51-673F-4832-9999-25CDC53E6210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,14 +11,15 @@
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
     <sheet name="Buổi 3" sheetId="2" r:id="rId2"/>
     <sheet name="Buổi 4" sheetId="3" r:id="rId3"/>
-    <sheet name="New" sheetId="4" r:id="rId4"/>
+    <sheet name="Buổi 5" sheetId="5" r:id="rId4"/>
+    <sheet name="New" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="897">
   <si>
     <t>English</t>
   </si>
@@ -1980,6 +1981,735 @@
   </si>
   <si>
     <t>lều</t>
+  </si>
+  <si>
+    <t>/desk/</t>
+  </si>
+  <si>
+    <t>bàn làm việc</t>
+  </si>
+  <si>
+    <t>The desk is near the window.</t>
+  </si>
+  <si>
+    <t>Cái bàn ở gần cửa sổ.</t>
+  </si>
+  <si>
+    <t>/sterz/</t>
+  </si>
+  <si>
+    <t>He walks up the stairs.</t>
+  </si>
+  <si>
+    <t>Anh ấy đi lên cầu thang.</t>
+  </si>
+  <si>
+    <t>/ˈbɪldɪŋ/</t>
+  </si>
+  <si>
+    <t>tòa nhà</t>
+  </si>
+  <si>
+    <t>The building is very tall.</t>
+  </si>
+  <si>
+    <t>Tòa nhà rất cao.</t>
+  </si>
+  <si>
+    <t>/mæp/</t>
+  </si>
+  <si>
+    <t>bản đồ</t>
+  </si>
+  <si>
+    <t>She looks at the map.</t>
+  </si>
+  <si>
+    <t>Cô ấy nhìn bản đồ.</t>
+  </si>
+  <si>
+    <t>/ˈoʊʃən/</t>
+  </si>
+  <si>
+    <t>đại dương</t>
+  </si>
+  <si>
+    <t>The ocean is calm today.</t>
+  </si>
+  <si>
+    <t>Biển hôm nay yên bình.</t>
+  </si>
+  <si>
+    <t>/biːtʃ/</t>
+  </si>
+  <si>
+    <t>bãi biển</t>
+  </si>
+  <si>
+    <t>They walk along the beach.</t>
+  </si>
+  <si>
+    <t>Họ đi dọc bãi biển.</t>
+  </si>
+  <si>
+    <t>/sænd/</t>
+  </si>
+  <si>
+    <t>cát</t>
+  </si>
+  <si>
+    <t>The sand is hot.</t>
+  </si>
+  <si>
+    <t>Cát rất nóng.</t>
+  </si>
+  <si>
+    <t>/ˈaɪtəm/</t>
+  </si>
+  <si>
+    <t>vật phẩm</t>
+  </si>
+  <si>
+    <t>This item is expensive.</t>
+  </si>
+  <si>
+    <t>Món đồ này đắt.</t>
+  </si>
+  <si>
+    <t>/dɪˈspleɪ keɪs/</t>
+  </si>
+  <si>
+    <t>tủ trưng bày</t>
+  </si>
+  <si>
+    <t>The watch is in the display case.</t>
+  </si>
+  <si>
+    <t>Chiếc đồng hồ ở trong tủ trưng bày.</t>
+  </si>
+  <si>
+    <t>/ɡʊdz/</t>
+  </si>
+  <si>
+    <t>Hàng hóa, đồ gia dụng</t>
+  </si>
+  <si>
+    <t>The store sells many goods.</t>
+  </si>
+  <si>
+    <t>Cửa hàng bán nhiều hàng hóa.</t>
+  </si>
+  <si>
+    <t>/ʃelf/</t>
+  </si>
+  <si>
+    <t>kệ</t>
+  </si>
+  <si>
+    <t>The books are on the shelf.</t>
+  </si>
+  <si>
+    <t>Sách ở trên kệ.</t>
+  </si>
+  <si>
+    <t>/ˈmɜːrtʃəndaɪs/</t>
+  </si>
+  <si>
+    <t>hàng hóa</t>
+  </si>
+  <si>
+    <t>They display merchandise.</t>
+  </si>
+  <si>
+    <t>Họ trưng bày hàng hóa.</t>
+  </si>
+  <si>
+    <t>/flɔːr/</t>
+  </si>
+  <si>
+    <t>sàn nhà</t>
+  </si>
+  <si>
+    <t>The floor is clean.</t>
+  </si>
+  <si>
+    <t>Sàn nhà sạch.</t>
+  </si>
+  <si>
+    <t>/fens/</t>
+  </si>
+  <si>
+    <t>hàng rào</t>
+  </si>
+  <si>
+    <t>The fence surrounds the house.</t>
+  </si>
+  <si>
+    <t>Hàng rào bao quanh nhà.</t>
+  </si>
+  <si>
+    <t>/ˈdʒækɪt/</t>
+  </si>
+  <si>
+    <t>áo khoác</t>
+  </si>
+  <si>
+    <t>He wears a jacket.</t>
+  </si>
+  <si>
+    <t>Anh ấy mặc áo khoác.</t>
+  </si>
+  <si>
+    <t>/ˈɡɑːrdn/</t>
+  </si>
+  <si>
+    <t>khu vườn</t>
+  </si>
+  <si>
+    <t>She works in the garden.</t>
+  </si>
+  <si>
+    <t>Cô ấy làm việc trong vườn.</t>
+  </si>
+  <si>
+    <t>/ˈkɑːrpɪt/</t>
+  </si>
+  <si>
+    <t>thảm</t>
+  </si>
+  <si>
+    <t>The carpet is soft.</t>
+  </si>
+  <si>
+    <t>Tấm thảm mềm.</t>
+  </si>
+  <si>
+    <t>/ˈkɜːrtn/</t>
+  </si>
+  <si>
+    <t>rèm cửa</t>
+  </si>
+  <si>
+    <t>The curtain is closed.</t>
+  </si>
+  <si>
+    <t>Rèm đã đóng.</t>
+  </si>
+  <si>
+    <t>/ˈkʊʃn/</t>
+  </si>
+  <si>
+    <t>gối (có đệm)</t>
+  </si>
+  <si>
+    <t>She sits on a cushion.</t>
+  </si>
+  <si>
+    <t>Cô ấy ngồi trên gối.</t>
+  </si>
+  <si>
+    <t>/ˈriːdɪŋ məˈtɪriəlz/</t>
+  </si>
+  <si>
+    <t>tài liệu đọc</t>
+  </si>
+  <si>
+    <t>He brings reading materials.</t>
+  </si>
+  <si>
+    <t>Anh ấy mang tài liệu đọc.</t>
+  </si>
+  <si>
+    <t>/pɔːrtʃ/</t>
+  </si>
+  <si>
+    <t>hiên nhà</t>
+  </si>
+  <si>
+    <t>They sit on the porch.</t>
+  </si>
+  <si>
+    <t>Họ ngồi ở hiên nhà.</t>
+  </si>
+  <si>
+    <t>/ˈmjuːzɪk stænd/</t>
+  </si>
+  <si>
+    <t>giá để nhạc</t>
+  </si>
+  <si>
+    <t>The notes are on the music stand.</t>
+  </si>
+  <si>
+    <t>Bản nhạc ở trên giá.</t>
+  </si>
+  <si>
+    <t>/ˈɪnstrəmənt/</t>
+  </si>
+  <si>
+    <t>nhạc cụ</t>
+  </si>
+  <si>
+    <t>She plays an instrument.</t>
+  </si>
+  <si>
+    <t>Cô ấy chơi nhạc cụ.</t>
+  </si>
+  <si>
+    <t>/ˈpaʊər tuːl/</t>
+  </si>
+  <si>
+    <t>dụng cụ điện</t>
+  </si>
+  <si>
+    <t>He uses a power tool.</t>
+  </si>
+  <si>
+    <t>Anh ấy dùng dụng cụ điện.</t>
+  </si>
+  <si>
+    <t>/drɔːr/</t>
+  </si>
+  <si>
+    <t>ngăn kéo</t>
+  </si>
+  <si>
+    <t>The drawer is open.</t>
+  </si>
+  <si>
+    <t>Ngăn kéo đang mở.</t>
+  </si>
+  <si>
+    <t>/ˈprɪntər/</t>
+  </si>
+  <si>
+    <t>máy in</t>
+  </si>
+  <si>
+    <t>The printer is working.</t>
+  </si>
+  <si>
+    <t>Máy in đang hoạt động.</t>
+  </si>
+  <si>
+    <t>/ˈɔːfɪs səˈplaɪz/</t>
+  </si>
+  <si>
+    <t>văn phòng phẩm</t>
+  </si>
+  <si>
+    <t>They buy office supplies.</t>
+  </si>
+  <si>
+    <t>Họ mua văn phòng phẩm.</t>
+  </si>
+  <si>
+    <t>/ˈʃɑːpɪŋ kɑːrt/</t>
+  </si>
+  <si>
+    <t>xe đẩy mua hàng</t>
+  </si>
+  <si>
+    <t>She pushes a shopping cart.</t>
+  </si>
+  <si>
+    <t>Cô ấy đẩy xe hàng.</t>
+  </si>
+  <si>
+    <t>/ˈwɔːtərɪŋ kæn/</t>
+  </si>
+  <si>
+    <t>bình tưới nước</t>
+  </si>
+  <si>
+    <t>He uses a watering can.</t>
+  </si>
+  <si>
+    <t>Anh ấy dùng bình tưới.</t>
+  </si>
+  <si>
+    <t>/ˈpɑːtɪd plænt/</t>
+  </si>
+  <si>
+    <t>cây trong chậu</t>
+  </si>
+  <si>
+    <t>The potted plant is green.</t>
+  </si>
+  <si>
+    <t>Cây trong chậu là xanh tươi.</t>
+  </si>
+  <si>
+    <t>/məˈʃiːn/</t>
+  </si>
+  <si>
+    <t>máy móc</t>
+  </si>
+  <si>
+    <t>The machine is noisy.</t>
+  </si>
+  <si>
+    <t>Máy rất ồn.</t>
+  </si>
+  <si>
+    <t>/ɪˈkwɪpmənt/</t>
+  </si>
+  <si>
+    <t>thiết bị</t>
+  </si>
+  <si>
+    <t>The equipment is new.</t>
+  </si>
+  <si>
+    <t>Thiết bị mới.</t>
+  </si>
+  <si>
+    <t>tạ</t>
+  </si>
+  <si>
+    <t>He lifts weights.</t>
+  </si>
+  <si>
+    <t>Anh ấy nâng tạ.</t>
+  </si>
+  <si>
+    <t>/ˈdʌmbel/</t>
+  </si>
+  <si>
+    <t>tạ tay</t>
+  </si>
+  <si>
+    <t>She holds a dumbbell.</t>
+  </si>
+  <si>
+    <t>Cô ấy cầm tạ tay.</t>
+  </si>
+  <si>
+    <t>/ˈbɑːrbel/</t>
+  </si>
+  <si>
+    <t>tạ đòn</t>
+  </si>
+  <si>
+    <t>He lifts a barbell.</t>
+  </si>
+  <si>
+    <t>Anh ấy nâng tạ đòn.</t>
+  </si>
+  <si>
+    <t>/ˈsiːlɪŋ/</t>
+  </si>
+  <si>
+    <t>trần nhà</t>
+  </si>
+  <si>
+    <t>The ceiling is high.</t>
+  </si>
+  <si>
+    <t>Trần nhà cao.</t>
+  </si>
+  <si>
+    <t>/wɔːl/</t>
+  </si>
+  <si>
+    <t>tường</t>
+  </si>
+  <si>
+    <t>The wall is white.</t>
+  </si>
+  <si>
+    <t>Bức tường màu trắng.</t>
+  </si>
+  <si>
+    <t>/ˈdɔːrweɪ/</t>
+  </si>
+  <si>
+    <t>cửa ra vào</t>
+  </si>
+  <si>
+    <t>He stands in the doorway.</t>
+  </si>
+  <si>
+    <t>Anh ấy đứng ở cửa.</t>
+  </si>
+  <si>
+    <t>/ˈstætʃuː/</t>
+  </si>
+  <si>
+    <t>tượng</t>
+  </si>
+  <si>
+    <t>The statue is large.</t>
+  </si>
+  <si>
+    <t>Bức tượng lớn.</t>
+  </si>
+  <si>
+    <t>bức tranh</t>
+  </si>
+  <si>
+    <t>The painting is beautiful.</t>
+  </si>
+  <si>
+    <t>Bức tranh đẹp.</t>
+  </si>
+  <si>
+    <t>/ɡɪft/</t>
+  </si>
+  <si>
+    <t>món quà</t>
+  </si>
+  <si>
+    <t>She gives a gift.</t>
+  </si>
+  <si>
+    <t>Cô ấy tặng quà.</t>
+  </si>
+  <si>
+    <t>/ˈtræfɪk koʊn/</t>
+  </si>
+  <si>
+    <t>cọc côn giao thông (cọc hình nón)</t>
+  </si>
+  <si>
+    <t>The traffic cone is on the road.</t>
+  </si>
+  <si>
+    <t>Cọc côn giao thông ở trên đường.</t>
+  </si>
+  <si>
+    <t>/sɔɪl/</t>
+  </si>
+  <si>
+    <t>đất</t>
+  </si>
+  <si>
+    <t>The soil is wet.</t>
+  </si>
+  <si>
+    <t>Đất là ướt.</t>
+  </si>
+  <si>
+    <t>/bʊʃ/</t>
+  </si>
+  <si>
+    <t>bụi cây</t>
+  </si>
+  <si>
+    <t>The bush is green.</t>
+  </si>
+  <si>
+    <t>Bụi cây xanh.</t>
+  </si>
+  <si>
+    <t>/koʊt/</t>
+  </si>
+  <si>
+    <t>He wears a coat.</t>
+  </si>
+  <si>
+    <t>/hɑːrd hæt/</t>
+  </si>
+  <si>
+    <t>mũ bảo hộ</t>
+  </si>
+  <si>
+    <t>He wears a hard hat.</t>
+  </si>
+  <si>
+    <t>Anh ấy đội mũ bảo hộ.</t>
+  </si>
+  <si>
+    <t>/ɡræs/</t>
+  </si>
+  <si>
+    <t>cỏ</t>
+  </si>
+  <si>
+    <t>The grass is fresh.</t>
+  </si>
+  <si>
+    <t>Cỏ tươi.</t>
+  </si>
+  <si>
+    <t>/ˈmɪrər/</t>
+  </si>
+  <si>
+    <t>gương</t>
+  </si>
+  <si>
+    <t>She looks in the mirror.</t>
+  </si>
+  <si>
+    <t>Cô ấy nhìn vào gương.</t>
+  </si>
+  <si>
+    <t>/ˈsterweɪ/</t>
+  </si>
+  <si>
+    <t>The stairway is narrow.</t>
+  </si>
+  <si>
+    <t>Cầu thang hẹp.</t>
+  </si>
+  <si>
+    <t>/ˈbæskɪt/</t>
+  </si>
+  <si>
+    <t>giỏ</t>
+  </si>
+  <si>
+    <t>She carries a basket.</t>
+  </si>
+  <si>
+    <t>Cô ấy mang giỏ.</t>
+  </si>
+  <si>
+    <t>desk</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>ocean</t>
+  </si>
+  <si>
+    <t>beach</t>
+  </si>
+  <si>
+    <t>sand</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>display case</t>
+  </si>
+  <si>
+    <t>goods</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>merchandise</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>fence</t>
+  </si>
+  <si>
+    <t>jacket</t>
+  </si>
+  <si>
+    <t>garden</t>
+  </si>
+  <si>
+    <t>carpet</t>
+  </si>
+  <si>
+    <t>curtain</t>
+  </si>
+  <si>
+    <t>cushion</t>
+  </si>
+  <si>
+    <t>reading materials</t>
+  </si>
+  <si>
+    <t>porch</t>
+  </si>
+  <si>
+    <t>music stand</t>
+  </si>
+  <si>
+    <t>instrument</t>
+  </si>
+  <si>
+    <t>power tool</t>
+  </si>
+  <si>
+    <t>drawer</t>
+  </si>
+  <si>
+    <t>printer</t>
+  </si>
+  <si>
+    <t>office supplies</t>
+  </si>
+  <si>
+    <t>shopping cart</t>
+  </si>
+  <si>
+    <t>watering can</t>
+  </si>
+  <si>
+    <t>potted plant</t>
+  </si>
+  <si>
+    <t>machine</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>dumbbell</t>
+  </si>
+  <si>
+    <t>barbell</t>
+  </si>
+  <si>
+    <t>ceiling</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>doorway</t>
+  </si>
+  <si>
+    <t>statue</t>
+  </si>
+  <si>
+    <t>painting</t>
+  </si>
+  <si>
+    <t>gift</t>
+  </si>
+  <si>
+    <t>traffic cone</t>
+  </si>
+  <si>
+    <t>soil</t>
+  </si>
+  <si>
+    <t>bush</t>
+  </si>
+  <si>
+    <t>coat</t>
+  </si>
+  <si>
+    <t>hard hat</t>
+  </si>
+  <si>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>mirror</t>
+  </si>
+  <si>
+    <t>stairway</t>
+  </si>
+  <si>
+    <t>basket</t>
   </si>
 </sst>
 </file>
@@ -5109,6 +5839,889 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7391CFE-FB58-4397-B398-8BFF6F9AA547}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>879</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>882</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB905D0-5FC0-49F8-9009-8F91F0A4360C}">
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/flashcard_template.xlsx
+++ b/flashcard_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC37B51-673F-4832-9999-25CDC53E6210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70F0531-3B12-4FB6-B097-DC7785B9EADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,14 +12,13 @@
     <sheet name="Buổi 3" sheetId="2" r:id="rId2"/>
     <sheet name="Buổi 4" sheetId="3" r:id="rId3"/>
     <sheet name="Buổi 5" sheetId="5" r:id="rId4"/>
-    <sheet name="New" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="890">
   <si>
     <t>English</t>
   </si>
@@ -1956,31 +1955,10 @@
     <t>row</t>
   </si>
   <si>
-    <t>shade</t>
-  </si>
-  <si>
-    <t>..</t>
-  </si>
-  <si>
-    <t>bóng mát</t>
-  </si>
-  <si>
     <t>stairs</t>
   </si>
   <si>
     <t>cầu thang</t>
-  </si>
-  <si>
-    <t>stage</t>
-  </si>
-  <si>
-    <t>sân khấu</t>
-  </si>
-  <si>
-    <t>tent</t>
-  </si>
-  <si>
-    <t>lều</t>
   </si>
   <si>
     <t>/desk/</t>
@@ -5868,1258 +5846,853 @@
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>280</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB905D0-5FC0-49F8-9009-8F91F0A4360C}">
-  <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="5" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="7"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+        <v>840</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
